--- a/03_ДЗ/ЛР-6/ЛР6_вар7.xlsx
+++ b/03_ДЗ/ЛР-6/ЛР6_вар7.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -148,17 +148,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -762,7 +759,7 @@
       </c>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="7" t="n"/>
-      <c r="K12" s="10" t="n">
+      <c r="K12" s="9" t="n">
         <v>148.6</v>
       </c>
     </row>
@@ -792,7 +789,7 @@
       </c>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
-      <c r="K13" s="11" t="n">
+      <c r="K13" s="9" t="n">
         <v>165.54</v>
       </c>
     </row>
@@ -838,7 +835,7 @@
       </c>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="7" t="n"/>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="10" t="n">
         <v>400</v>
       </c>
       <c r="G15" s="6" t="n">
@@ -859,7 +856,7 @@
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Кзап = 1,4</t>
         </is>
@@ -876,102 +873,102 @@
       </c>
       <c r="I16" s="7" t="n"/>
       <c r="J16" s="7" t="n"/>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="12" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14">
+      <c r="A23" s="13">
         <f>A1</f>
         <v/>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Результаты расчета</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Фамилия</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>......................</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <f>B6</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>секция
 показатели</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>НК</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="19" t="n">
+      <c r="E27" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G27" s="19" t="n">
+      <c r="G27" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="19" t="n">
+      <c r="H27" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="I27" s="19" t="n">
+      <c r="I27" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="J27" s="19" t="n">
+      <c r="J27" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="K27" s="19" t="n">
+      <c r="K27" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="L27" s="19" t="n">
+      <c r="L27" s="18" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Тип труб</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>ТБВК</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>ТБВК</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>ТБВК</t>
         </is>
@@ -986,19 +983,19 @@
       <c r="L28" s="7" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Толщина стенок,
 м</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="19" t="n">
         <v>0.01</v>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="19" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="19" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="E29" s="7" t="n"/>
@@ -1011,23 +1008,23 @@
       <c r="L29" s="7" t="n"/>
     </row>
     <row r="30" ht="33" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Группа прочности
 стали</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>д</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>к</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>е</t>
         </is>
@@ -1042,22 +1039,22 @@
       <c r="L30" s="7" t="n"/>
     </row>
     <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Предельно
 растягивающая
 нагрузка, 10⁴ Н</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C31" s="19" t="n">
         <v>167</v>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="19" t="n">
         <v>184</v>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1070,19 +1067,19 @@
       <c r="L31" s="7" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Масса 1 м трубы,
 кг</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n">
+      <c r="B32" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="C32" s="21" t="n">
+      <c r="C32" s="20" t="n">
         <v>29.3</v>
       </c>
-      <c r="D32" s="21" t="n">
+      <c r="D32" s="20" t="n">
         <v>29.3</v>
       </c>
       <c r="E32" s="7" t="n"/>
@@ -1095,82 +1092,82 @@
       <c r="L32" s="7" t="n"/>
     </row>
     <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Площадь попереч.
 сечения канала
 труб, м²</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C33" s="21" t="n">
+      <c r="C33" s="20" t="n">
         <v>93.3</v>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G33" s="20" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H33" s="20" t="inlineStr">
+      <c r="H33" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="20" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J33" s="20" t="inlineStr">
+      <c r="J33" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K33" s="20" t="inlineStr">
+      <c r="K33" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L33" s="20" t="inlineStr">
+      <c r="L33" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Длина секции, м</t>
         </is>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="21">
         <f>E15</f>
         <v/>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="22">
         <f>(0.8*C31*10^4/1.4-1.1*($K$13+B36)*1000-($K$16+$K$14)*10^6*C33*10^-4)/(1.1*9.81*C32*(1-$K$11/$K$10))</f>
         <v/>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="22">
         <f>(0.8*D31*10^4/1.4-0.8*C31*10^4/1.4)/(1.1*9.81*D32*(1-$K$11/$K$10))</f>
         <v/>
       </c>
@@ -1184,21 +1181,21 @@
       <c r="L34" s="7" t="n"/>
     </row>
     <row r="35" ht="33" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Уточненная длина
 секции, м</t>
         </is>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="22">
         <f>B34</f>
         <v/>
       </c>
-      <c r="C35" s="23">
+      <c r="C35" s="22">
         <f>IF(B37+C34&gt;$E$12,$E$12-B37,IF(C34&lt;250,"выберите трубы с большей прочностью",FLOOR(C34,25)))</f>
         <v/>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="22">
         <f>IF(C37+D34&gt;$E$12,$E$12-C37,IF(D34&lt;250,"выберите трубы с большей прочностью",FLOOR(D34,25)))</f>
         <v/>
       </c>
@@ -1212,20 +1209,20 @@
       <c r="L35" s="7" t="n"/>
     </row>
     <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Вес, кН</t>
         </is>
       </c>
-      <c r="B36" s="23">
+      <c r="B36" s="22">
         <f>9.81*B35*B32*(1-$K$11/$K$10)/1000</f>
         <v/>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="22">
         <f>9.81*C35*C32*(1-$K$11/$K$10)/1000</f>
         <v/>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="22">
         <f>9.81*D35*D32*(1-$K$11/$K$10)/1000</f>
         <v/>
       </c>
@@ -1239,22 +1236,22 @@
       <c r="L36" s="7" t="n"/>
     </row>
     <row r="37" ht="33" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Нарастающая
 длина
 по секциям, м</t>
         </is>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="22">
         <f>K12+B35</f>
         <v/>
       </c>
-      <c r="C37" s="23">
+      <c r="C37" s="22">
         <f>B37+C35</f>
         <v/>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="22">
         <f>C37+D35</f>
         <v/>
       </c>
@@ -1268,21 +1265,21 @@
       <c r="L37" s="7" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Общий вес
 колонны, кН</t>
         </is>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="22">
         <f>K13+B36</f>
         <v/>
       </c>
-      <c r="C38" s="23">
+      <c r="C38" s="22">
         <f>B38+C36</f>
         <v/>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="22">
         <f>C38+D36</f>
         <v/>
       </c>
@@ -1296,18 +1293,18 @@
       <c r="L38" s="7" t="n"/>
     </row>
     <row r="39" ht="35" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Длина
 инструмента
 в целом, м</t>
         </is>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="22">
         <f>D37</f>
         <v/>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="19">
         <f>IF(ROUND(B39,2)=E12,"Расчет завершен.","")</f>
         <v/>
       </c>
